--- a/tinHelm/excel/Role.xlsx
+++ b/tinHelm/excel/Role.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21555" windowHeight="6825"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -46,6 +46,12 @@
     <t>角色信息</t>
   </si>
   <si>
+    <t>初始血量</t>
+  </si>
+  <si>
+    <t>血量上限</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -56,6 +62,12 @@
   </si>
   <si>
     <t>info</t>
+  </si>
+  <si>
+    <t>originHp</t>
+  </si>
+  <si>
+    <t>maxHp</t>
   </si>
   <si>
     <t>int</t>
@@ -107,14 +119,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,148 +575,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1063,15 +1068,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1084,103 +1089,151 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1001</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1002</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/tinHelm/excel/Role.xlsx
+++ b/tinHelm/excel/Role.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -52,6 +52,9 @@
     <t>血量上限</t>
   </si>
   <si>
+    <t>初始卡牌</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -70,12 +73,18 @@
     <t>maxHp</t>
   </si>
   <si>
+    <t>originCards</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>array</t>
+  </si>
+  <si>
     <t>server</t>
   </si>
   <si>
@@ -91,6 +100,9 @@
     <t>稳定的攻防角色，善于把冠面转化为护甲与追加伤害，适合第一局体验。</t>
   </si>
   <si>
+    <t>[2001,2002,2003]</t>
+  </si>
+  <si>
     <t>刃少女</t>
   </si>
   <si>
@@ -100,6 +112,9 @@
     <t>偏向连续攻击与重掷，能快速打出多段小伤害，但防御更依赖操作节奏。</t>
   </si>
   <si>
+    <t>[2004,2005,2006]</t>
+  </si>
+  <si>
     <t>咒术游侠</t>
   </si>
   <si>
@@ -107,6 +122,9 @@
   </si>
   <si>
     <t>擅长资源和防御控制，可以更稳定地进入后期，依赖技能卡组合获胜。</t>
+  </si>
+  <si>
+    <t>[2007,2008,2009]</t>
   </si>
 </sst>
 </file>
@@ -1068,15 +1086,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1095,99 +1113,114 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1001</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -1195,19 +1228,22 @@
       <c r="F6">
         <v>100</v>
       </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1002</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -1215,25 +1251,31 @@
       <c r="F7">
         <v>80</v>
       </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>90</v>
       </c>
       <c r="F8">
         <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
